--- a/review-results/河北实时运行及市场出清数据-20260904.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260904.xlsx
@@ -4284,7 +4284,9 @@
       <s:c r="C2" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="1"/>
+      <s:c r="D2" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E2" s="1" t="n">
         <s:v>414.11</s:v>
       </s:c>
@@ -4332,7 +4334,9 @@
       <s:c r="C3" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="1"/>
+      <s:c r="D3" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E3" s="1" t="n">
         <s:v>412.97</s:v>
       </s:c>
@@ -4380,7 +4384,9 @@
       <s:c r="C4" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="1"/>
+      <s:c r="D4" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E4" s="1" t="n">
         <s:v>409.23</s:v>
       </s:c>
@@ -4428,7 +4434,9 @@
       <s:c r="C5" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="1"/>
+      <s:c r="D5" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E5" s="1" t="n">
         <s:v>413.29</s:v>
       </s:c>
@@ -4476,7 +4484,9 @@
       <s:c r="C6" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="1"/>
+      <s:c r="D6" s="1" t="n">
+        <s:v>345.5</s:v>
+      </s:c>
       <s:c r="E6" s="1" t="n">
         <s:v>415.08</s:v>
       </s:c>
@@ -4524,7 +4534,9 @@
       <s:c r="C7" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="1"/>
+      <s:c r="D7" s="1" t="n">
+        <s:v>345.5</s:v>
+      </s:c>
       <s:c r="E7" s="1" t="n">
         <s:v>412.01</s:v>
       </s:c>
@@ -4572,7 +4584,9 @@
       <s:c r="C8" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="1"/>
+      <s:c r="D8" s="1" t="n">
+        <s:v>345.5</s:v>
+      </s:c>
       <s:c r="E8" s="1" t="n">
         <s:v>405.2</s:v>
       </s:c>
@@ -4620,7 +4634,9 @@
       <s:c r="C9" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="1"/>
+      <s:c r="D9" s="1" t="n">
+        <s:v>351.14</s:v>
+      </s:c>
       <s:c r="E9" s="1" t="n">
         <s:v>397.36</s:v>
       </s:c>
@@ -4668,7 +4684,9 @@
       <s:c r="C10" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="1"/>
+      <s:c r="D10" s="1" t="n">
+        <s:v>351.14</s:v>
+      </s:c>
       <s:c r="E10" s="1" t="n">
         <s:v>401.69</s:v>
       </s:c>
@@ -4716,7 +4734,9 @@
       <s:c r="C11" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="1"/>
+      <s:c r="D11" s="1" t="n">
+        <s:v>351.14</s:v>
+      </s:c>
       <s:c r="E11" s="1" t="n">
         <s:v>411.85</s:v>
       </s:c>
@@ -4764,7 +4784,9 @@
       <s:c r="C12" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="1"/>
+      <s:c r="D12" s="1" t="n">
+        <s:v>351.14</s:v>
+      </s:c>
       <s:c r="E12" s="1" t="n">
         <s:v>403.22</s:v>
       </s:c>
@@ -4812,7 +4834,9 @@
       <s:c r="C13" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="1"/>
+      <s:c r="D13" s="1" t="n">
+        <s:v>345.5</s:v>
+      </s:c>
       <s:c r="E13" s="1" t="n">
         <s:v>396.26</s:v>
       </s:c>
@@ -4860,7 +4884,9 @@
       <s:c r="C14" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="1"/>
+      <s:c r="D14" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E14" s="1" t="n">
         <s:v>403.35</s:v>
       </s:c>
@@ -4908,7 +4934,9 @@
       <s:c r="C15" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="1"/>
+      <s:c r="D15" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E15" s="1" t="n">
         <s:v>396.26</s:v>
       </s:c>
@@ -4956,7 +4984,9 @@
       <s:c r="C16" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="1"/>
+      <s:c r="D16" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E16" s="1" t="n">
         <s:v>397.64</s:v>
       </s:c>
@@ -5004,7 +5034,9 @@
       <s:c r="C17" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="1"/>
+      <s:c r="D17" s="1" t="n">
+        <s:v>345.5</s:v>
+      </s:c>
       <s:c r="E17" s="1" t="n">
         <s:v>403.89</s:v>
       </s:c>
@@ -5052,7 +5084,9 @@
       <s:c r="C18" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="1"/>
+      <s:c r="D18" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E18" s="1" t="n">
         <s:v>403.22</s:v>
       </s:c>
@@ -5100,7 +5134,9 @@
       <s:c r="C19" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="1"/>
+      <s:c r="D19" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E19" s="1" t="n">
         <s:v>403.35</s:v>
       </s:c>
@@ -5148,7 +5184,9 @@
       <s:c r="C20" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="1"/>
+      <s:c r="D20" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E20" s="1" t="n">
         <s:v>403.35</s:v>
       </s:c>
@@ -5196,7 +5234,9 @@
       <s:c r="C21" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="1"/>
+      <s:c r="D21" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E21" s="1" t="n">
         <s:v>403.47</s:v>
       </s:c>
@@ -5244,7 +5284,9 @@
       <s:c r="C22" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="1"/>
+      <s:c r="D22" s="1" t="n">
+        <s:v>369.79</s:v>
+      </s:c>
       <s:c r="E22" s="1" t="n">
         <s:v>403.47</s:v>
       </s:c>
@@ -5292,7 +5334,9 @@
       <s:c r="C23" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="1"/>
+      <s:c r="D23" s="1" t="n">
+        <s:v>369.79</s:v>
+      </s:c>
       <s:c r="E23" s="1" t="n">
         <s:v>410.83</s:v>
       </s:c>
@@ -5340,7 +5384,9 @@
       <s:c r="C24" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="1"/>
+      <s:c r="D24" s="1" t="n">
+        <s:v>369.79</s:v>
+      </s:c>
       <s:c r="E24" s="1" t="n">
         <s:v>413.45</s:v>
       </s:c>
@@ -5388,7 +5434,9 @@
       <s:c r="C25" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="1"/>
+      <s:c r="D25" s="1" t="n">
+        <s:v>369.79</s:v>
+      </s:c>
       <s:c r="E25" s="1" t="n">
         <s:v>413.45</s:v>
       </s:c>
@@ -5436,7 +5484,9 @@
       <s:c r="C26" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="1"/>
+      <s:c r="D26" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E26" s="1" t="n">
         <s:v>406.41</s:v>
       </s:c>
@@ -5484,7 +5534,9 @@
       <s:c r="C27" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="1"/>
+      <s:c r="D27" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E27" s="1" t="n">
         <s:v>403.6</s:v>
       </s:c>
@@ -5532,7 +5584,9 @@
       <s:c r="C28" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="1"/>
+      <s:c r="D28" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E28" s="1" t="n">
         <s:v>404.86</s:v>
       </s:c>
@@ -5580,7 +5634,9 @@
       <s:c r="C29" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="1"/>
+      <s:c r="D29" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E29" s="1" t="n">
         <s:v>397.36</s:v>
       </s:c>
@@ -5628,7 +5684,9 @@
       <s:c r="C30" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="1"/>
+      <s:c r="D30" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E30" s="1" t="n">
         <s:v>402.5</s:v>
       </s:c>
@@ -5676,7 +5734,9 @@
       <s:c r="C31" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="1"/>
+      <s:c r="D31" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E31" s="1" t="n">
         <s:v>396.39</s:v>
       </s:c>
@@ -5724,7 +5784,9 @@
       <s:c r="C32" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="1"/>
+      <s:c r="D32" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E32" s="1" t="n">
         <s:v>389.26</s:v>
       </s:c>
@@ -5772,7 +5834,9 @@
       <s:c r="C33" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="1"/>
+      <s:c r="D33" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E33" s="1" t="n">
         <s:v>381.01</s:v>
       </s:c>
@@ -5820,7 +5884,9 @@
       <s:c r="C34" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="1"/>
+      <s:c r="D34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E34" s="1" t="n">
         <s:v>379.47</s:v>
       </s:c>
@@ -5868,7 +5934,9 @@
       <s:c r="C35" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="1"/>
+      <s:c r="D35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E35" s="1" t="n">
         <s:v>371.14</s:v>
       </s:c>
@@ -5916,7 +5984,9 @@
       <s:c r="C36" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="1"/>
+      <s:c r="D36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E36" s="1" t="n">
         <s:v>357.01</s:v>
       </s:c>
@@ -5964,7 +6034,9 @@
       <s:c r="C37" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="1"/>
+      <s:c r="D37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E37" s="1" t="n">
         <s:v>348.76</s:v>
       </s:c>
@@ -6012,7 +6084,9 @@
       <s:c r="C38" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="1"/>
+      <s:c r="D38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E38" s="1" t="n">
         <s:v>348.42</s:v>
       </s:c>
@@ -6060,7 +6134,9 @@
       <s:c r="C39" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="1"/>
+      <s:c r="D39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E39" s="1" t="n">
         <s:v>349.05</s:v>
       </s:c>
@@ -6108,7 +6184,9 @@
       <s:c r="C40" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="1"/>
+      <s:c r="D40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E40" s="1" t="n">
         <s:v>350</s:v>
       </s:c>
@@ -6156,7 +6234,9 @@
       <s:c r="C41" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="1"/>
+      <s:c r="D41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E41" s="1" t="n">
         <s:v>349.33</s:v>
       </s:c>
@@ -6204,7 +6284,9 @@
       <s:c r="C42" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="1"/>
+      <s:c r="D42" s="1" t="n">
+        <s:v>330.44</s:v>
+      </s:c>
       <s:c r="E42" s="1" t="n">
         <s:v>349.54</s:v>
       </s:c>
@@ -6252,7 +6334,9 @@
       <s:c r="C43" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="1"/>
+      <s:c r="D43" s="1" t="n">
+        <s:v>330.44</s:v>
+      </s:c>
       <s:c r="E43" s="1" t="n">
         <s:v>348.85</s:v>
       </s:c>
@@ -6300,7 +6384,9 @@
       <s:c r="C44" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="1"/>
+      <s:c r="D44" s="1" t="n">
+        <s:v>330.44</s:v>
+      </s:c>
       <s:c r="E44" s="1" t="n">
         <s:v>346.39</s:v>
       </s:c>
@@ -6348,7 +6434,9 @@
       <s:c r="C45" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="1"/>
+      <s:c r="D45" s="1" t="n">
+        <s:v>330.44</s:v>
+      </s:c>
       <s:c r="E45" s="1" t="n">
         <s:v>350</s:v>
       </s:c>
@@ -6396,7 +6484,9 @@
       <s:c r="C46" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="1"/>
+      <s:c r="D46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E46" s="1" t="n">
         <s:v>349.33</s:v>
       </s:c>
@@ -6444,7 +6534,9 @@
       <s:c r="C47" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="1"/>
+      <s:c r="D47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E47" s="1" t="n">
         <s:v>430.32</s:v>
       </s:c>
@@ -6492,7 +6584,9 @@
       <s:c r="C48" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="1"/>
+      <s:c r="D48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E48" s="1" t="n">
         <s:v>365.5</s:v>
       </s:c>
@@ -6540,7 +6634,9 @@
       <s:c r="C49" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="1"/>
+      <s:c r="D49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E49" s="1" t="n">
         <s:v>348.76</s:v>
       </s:c>
@@ -6588,7 +6684,9 @@
       <s:c r="C50" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="1"/>
+      <s:c r="D50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E50" s="1" t="n">
         <s:v>343.01</s:v>
       </s:c>
@@ -6636,7 +6734,9 @@
       <s:c r="C51" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="1"/>
+      <s:c r="D51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E51" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6684,7 +6784,9 @@
       <s:c r="C52" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="1"/>
+      <s:c r="D52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E52" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6732,7 +6834,9 @@
       <s:c r="C53" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="1"/>
+      <s:c r="D53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E53" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6780,7 +6884,9 @@
       <s:c r="C54" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="1"/>
+      <s:c r="D54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E54" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6828,7 +6934,9 @@
       <s:c r="C55" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="1"/>
+      <s:c r="D55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E55" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6876,7 +6984,9 @@
       <s:c r="C56" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="1"/>
+      <s:c r="D56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E56" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6924,7 +7034,9 @@
       <s:c r="C57" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="1"/>
+      <s:c r="D57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E57" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6972,7 +7084,9 @@
       <s:c r="C58" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="1"/>
+      <s:c r="D58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E58" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7020,7 +7134,9 @@
       <s:c r="C59" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="1"/>
+      <s:c r="D59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E59" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7068,7 +7184,9 @@
       <s:c r="C60" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="1"/>
+      <s:c r="D60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E60" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7116,7 +7234,9 @@
       <s:c r="C61" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="1"/>
+      <s:c r="D61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E61" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7164,7 +7284,9 @@
       <s:c r="C62" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="1"/>
+      <s:c r="D62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E62" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7212,7 +7334,9 @@
       <s:c r="C63" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="1"/>
+      <s:c r="D63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E63" s="1" t="n">
         <s:v>348.76</s:v>
       </s:c>
@@ -7260,7 +7384,9 @@
       <s:c r="C64" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="1"/>
+      <s:c r="D64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E64" s="1" t="n">
         <s:v>198.32</s:v>
       </s:c>
@@ -7308,7 +7434,9 @@
       <s:c r="C65" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="1"/>
+      <s:c r="D65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
       <s:c r="E65" s="1" t="n">
         <s:v>198.32</s:v>
       </s:c>
@@ -7356,7 +7484,9 @@
       <s:c r="C66" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="1"/>
+      <s:c r="D66" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E66" s="1" t="n">
         <s:v>364.61</s:v>
       </s:c>
@@ -7404,7 +7534,9 @@
       <s:c r="C67" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="1"/>
+      <s:c r="D67" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E67" s="1" t="n">
         <s:v>373.77</s:v>
       </s:c>
@@ -7452,7 +7584,9 @@
       <s:c r="C68" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="1"/>
+      <s:c r="D68" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E68" s="1" t="n">
         <s:v>380.07</s:v>
       </s:c>
@@ -7500,7 +7634,9 @@
       <s:c r="C69" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="1"/>
+      <s:c r="D69" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E69" s="1" t="n">
         <s:v>387.14</s:v>
       </s:c>
@@ -7548,7 +7684,9 @@
       <s:c r="C70" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="1"/>
+      <s:c r="D70" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E70" s="1" t="n">
         <s:v>410.83</s:v>
       </s:c>
@@ -7596,7 +7734,9 @@
       <s:c r="C71" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="1"/>
+      <s:c r="D71" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E71" s="1" t="n">
         <s:v>413.32</s:v>
       </s:c>
@@ -7644,7 +7784,9 @@
       <s:c r="C72" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="1"/>
+      <s:c r="D72" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E72" s="1" t="n">
         <s:v>420.5</s:v>
       </s:c>
@@ -7692,7 +7834,9 @@
       <s:c r="C73" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="1"/>
+      <s:c r="D73" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E73" s="1" t="n">
         <s:v>421.58</s:v>
       </s:c>
@@ -7740,7 +7884,9 @@
       <s:c r="C74" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="1"/>
+      <s:c r="D74" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E74" s="1" t="n">
         <s:v>413.94</s:v>
       </s:c>
@@ -7788,7 +7934,9 @@
       <s:c r="C75" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="1"/>
+      <s:c r="D75" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E75" s="1" t="n">
         <s:v>421.1</s:v>
       </s:c>
@@ -7836,7 +7984,9 @@
       <s:c r="C76" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="1"/>
+      <s:c r="D76" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E76" s="1" t="n">
         <s:v>420.5</s:v>
       </s:c>
@@ -7884,7 +8034,9 @@
       <s:c r="C77" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="1"/>
+      <s:c r="D77" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E77" s="1" t="n">
         <s:v>413.64</s:v>
       </s:c>
@@ -7932,7 +8084,9 @@
       <s:c r="C78" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="1"/>
+      <s:c r="D78" s="1" t="n">
+        <s:v>369.79</s:v>
+      </s:c>
       <s:c r="E78" s="1" t="n">
         <s:v>421.89</s:v>
       </s:c>
@@ -7980,7 +8134,9 @@
       <s:c r="C79" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="1"/>
+      <s:c r="D79" s="1" t="n">
+        <s:v>369.79</s:v>
+      </s:c>
       <s:c r="E79" s="1" t="n">
         <s:v>417.16</s:v>
       </s:c>
@@ -8028,7 +8184,9 @@
       <s:c r="C80" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="1"/>
+      <s:c r="D80" s="1" t="n">
+        <s:v>369.79</s:v>
+      </s:c>
       <s:c r="E80" s="1" t="n">
         <s:v>402.85</s:v>
       </s:c>
@@ -8076,7 +8234,9 @@
       <s:c r="C81" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="1"/>
+      <s:c r="D81" s="1" t="n">
+        <s:v>361.85</s:v>
+      </s:c>
       <s:c r="E81" s="1" t="n">
         <s:v>403.35</s:v>
       </s:c>
@@ -8124,7 +8284,9 @@
       <s:c r="C82" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="1"/>
+      <s:c r="D82" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E82" s="1" t="n">
         <s:v>409.55</s:v>
       </s:c>
@@ -8172,7 +8334,9 @@
       <s:c r="C83" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="1"/>
+      <s:c r="D83" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E83" s="1" t="n">
         <s:v>404.29</s:v>
       </s:c>
@@ -8220,7 +8384,9 @@
       <s:c r="C84" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="1"/>
+      <s:c r="D84" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E84" s="1" t="n">
         <s:v>397.66</s:v>
       </s:c>
@@ -8268,7 +8434,9 @@
       <s:c r="C85" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="1"/>
+      <s:c r="D85" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E85" s="1" t="n">
         <s:v>396.22</s:v>
       </s:c>
@@ -8316,7 +8484,9 @@
       <s:c r="C86" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="1"/>
+      <s:c r="D86" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E86" s="1" t="n">
         <s:v>397.66</s:v>
       </s:c>
@@ -8364,7 +8534,9 @@
       <s:c r="C87" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="1"/>
+      <s:c r="D87" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E87" s="1" t="n">
         <s:v>397.58</s:v>
       </s:c>
@@ -8412,7 +8584,9 @@
       <s:c r="C88" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="1"/>
+      <s:c r="D88" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E88" s="1" t="n">
         <s:v>398.85</s:v>
       </s:c>
@@ -8460,7 +8634,9 @@
       <s:c r="C89" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="1"/>
+      <s:c r="D89" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E89" s="1" t="n">
         <s:v>396.55</s:v>
       </s:c>
@@ -8508,7 +8684,9 @@
       <s:c r="C90" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="1"/>
+      <s:c r="D90" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E90" s="1" t="n">
         <s:v>403.22</s:v>
       </s:c>
@@ -8556,7 +8734,9 @@
       <s:c r="C91" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="1"/>
+      <s:c r="D91" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E91" s="1" t="n">
         <s:v>404.29</s:v>
       </s:c>
@@ -8604,7 +8784,9 @@
       <s:c r="C92" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="1"/>
+      <s:c r="D92" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E92" s="1" t="n">
         <s:v>406.41</s:v>
       </s:c>
@@ -8652,7 +8834,9 @@
       <s:c r="C93" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="1"/>
+      <s:c r="D93" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E93" s="1" t="n">
         <s:v>405.2</s:v>
       </s:c>
@@ -8700,7 +8884,9 @@
       <s:c r="C94" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="1"/>
+      <s:c r="D94" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E94" s="1" t="n">
         <s:v>406.41</s:v>
       </s:c>
@@ -8748,7 +8934,9 @@
       <s:c r="C95" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="1"/>
+      <s:c r="D95" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E95" s="1" t="n">
         <s:v>397.79</s:v>
       </s:c>
@@ -8796,7 +8984,9 @@
       <s:c r="C96" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="1"/>
+      <s:c r="D96" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E96" s="1" t="n">
         <s:v>399</s:v>
       </s:c>
@@ -8846,7 +9036,9 @@
       <s:c r="C97" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="1"/>
+      <s:c r="D97" s="1" t="n">
+        <s:v>343.01</s:v>
+      </s:c>
       <s:c r="E97" s="1" t="n">
         <s:v>404.42</s:v>
       </s:c>

--- a/review-results/河北实时运行及市场出清数据-20260904.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260904.xlsx
@@ -1403,9 +1403,7 @@
       <s:c r="D2" s="12" t="n">
         <s:v>29688.4</s:v>
       </s:c>
-      <s:c r="E2" s="13" t="n">
-        <s:v>8424.55</s:v>
-      </s:c>
+      <s:c r="E2" s="13"/>
       <s:c r="F2" s="14" t="n">
         <s:v>1099.4</s:v>
       </s:c>
@@ -1431,9 +1429,7 @@
       <s:c r="D3" s="12" t="n">
         <s:v>29374.4</s:v>
       </s:c>
-      <s:c r="E3" s="13" t="n">
-        <s:v>8416.93</s:v>
-      </s:c>
+      <s:c r="E3" s="13"/>
       <s:c r="F3" s="14" t="n">
         <s:v>1102.9</s:v>
       </s:c>
@@ -1459,9 +1455,7 @@
       <s:c r="D4" s="12" t="n">
         <s:v>29136.7</s:v>
       </s:c>
-      <s:c r="E4" s="13" t="n">
-        <s:v>8408.02</s:v>
-      </s:c>
+      <s:c r="E4" s="13"/>
       <s:c r="F4" s="14" t="n">
         <s:v>1112.6</s:v>
       </s:c>
@@ -1487,9 +1481,7 @@
       <s:c r="D5" s="12" t="n">
         <s:v>29083.2</s:v>
       </s:c>
-      <s:c r="E5" s="13" t="n">
-        <s:v>8397.79</s:v>
-      </s:c>
+      <s:c r="E5" s="13"/>
       <s:c r="F5" s="14" t="n">
         <s:v>1048.3</s:v>
       </s:c>
@@ -1515,9 +1507,7 @@
       <s:c r="D6" s="12" t="n">
         <s:v>28945.2</s:v>
       </s:c>
-      <s:c r="E6" s="13" t="n">
-        <s:v>8388.36</s:v>
-      </s:c>
+      <s:c r="E6" s="13"/>
       <s:c r="F6" s="14" t="n">
         <s:v>1014.8</s:v>
       </s:c>
@@ -1543,9 +1533,7 @@
       <s:c r="D7" s="12" t="n">
         <s:v>28797.6</s:v>
       </s:c>
-      <s:c r="E7" s="13" t="n">
-        <s:v>8382.89</s:v>
-      </s:c>
+      <s:c r="E7" s="13"/>
       <s:c r="F7" s="14" t="n">
         <s:v>967.5</s:v>
       </s:c>
@@ -1571,9 +1559,7 @@
       <s:c r="D8" s="12" t="n">
         <s:v>28523.7</s:v>
       </s:c>
-      <s:c r="E8" s="13" t="n">
-        <s:v>8377.1</s:v>
-      </s:c>
+      <s:c r="E8" s="13"/>
       <s:c r="F8" s="14" t="n">
         <s:v>927.6</s:v>
       </s:c>
@@ -1599,9 +1585,7 @@
       <s:c r="D9" s="12" t="n">
         <s:v>28777.8</s:v>
       </s:c>
-      <s:c r="E9" s="13" t="n">
-        <s:v>8371.96</s:v>
-      </s:c>
+      <s:c r="E9" s="13"/>
       <s:c r="F9" s="14" t="n">
         <s:v>864.4</s:v>
       </s:c>
@@ -1627,9 +1611,7 @@
       <s:c r="D10" s="12" t="n">
         <s:v>31474.5</s:v>
       </s:c>
-      <s:c r="E10" s="13" t="n">
-        <s:v>8363.99</s:v>
-      </s:c>
+      <s:c r="E10" s="13"/>
       <s:c r="F10" s="14" t="n">
         <s:v>831.6</s:v>
       </s:c>
@@ -1655,9 +1637,7 @@
       <s:c r="D11" s="12" t="n">
         <s:v>31312.5</s:v>
       </s:c>
-      <s:c r="E11" s="13" t="n">
-        <s:v>8356.4</s:v>
-      </s:c>
+      <s:c r="E11" s="13"/>
       <s:c r="F11" s="14" t="n">
         <s:v>823.6</s:v>
       </s:c>
@@ -1683,9 +1663,7 @@
       <s:c r="D12" s="12" t="n">
         <s:v>30712.6</s:v>
       </s:c>
-      <s:c r="E12" s="13" t="n">
-        <s:v>8349.51</s:v>
-      </s:c>
+      <s:c r="E12" s="13"/>
       <s:c r="F12" s="14" t="n">
         <s:v>816.9</s:v>
       </s:c>
@@ -1711,9 +1689,7 @@
       <s:c r="D13" s="12" t="n">
         <s:v>29991.9</s:v>
       </s:c>
-      <s:c r="E13" s="13" t="n">
-        <s:v>8343.21</s:v>
-      </s:c>
+      <s:c r="E13" s="13"/>
       <s:c r="F13" s="14" t="n">
         <s:v>804.3</s:v>
       </s:c>
@@ -1739,9 +1715,7 @@
       <s:c r="D14" s="12" t="n">
         <s:v>29579.1</s:v>
       </s:c>
-      <s:c r="E14" s="13" t="n">
-        <s:v>8339.18</s:v>
-      </s:c>
+      <s:c r="E14" s="13"/>
       <s:c r="F14" s="14" t="n">
         <s:v>793.3</s:v>
       </s:c>
@@ -1767,9 +1741,7 @@
       <s:c r="D15" s="12" t="n">
         <s:v>29369</s:v>
       </s:c>
-      <s:c r="E15" s="13" t="n">
-        <s:v>8334.05</s:v>
-      </s:c>
+      <s:c r="E15" s="13"/>
       <s:c r="F15" s="14" t="n">
         <s:v>780.1</s:v>
       </s:c>
@@ -1795,9 +1767,7 @@
       <s:c r="D16" s="12" t="n">
         <s:v>29180.9</s:v>
       </s:c>
-      <s:c r="E16" s="13" t="n">
-        <s:v>8329.36</s:v>
-      </s:c>
+      <s:c r="E16" s="13"/>
       <s:c r="F16" s="14" t="n">
         <s:v>772.3</s:v>
       </s:c>
@@ -1823,9 +1793,7 @@
       <s:c r="D17" s="12" t="n">
         <s:v>28947.5</s:v>
       </s:c>
-      <s:c r="E17" s="13" t="n">
-        <s:v>8325.75</s:v>
-      </s:c>
+      <s:c r="E17" s="13"/>
       <s:c r="F17" s="14" t="n">
         <s:v>759.1</s:v>
       </s:c>
@@ -1851,9 +1819,7 @@
       <s:c r="D18" s="12" t="n">
         <s:v>28671.8</s:v>
       </s:c>
-      <s:c r="E18" s="13" t="n">
-        <s:v>8333.85</s:v>
-      </s:c>
+      <s:c r="E18" s="13"/>
       <s:c r="F18" s="14" t="n">
         <s:v>756.9</s:v>
       </s:c>
@@ -1879,9 +1845,7 @@
       <s:c r="D19" s="12" t="n">
         <s:v>28547.2</s:v>
       </s:c>
-      <s:c r="E19" s="13" t="n">
-        <s:v>8331.05</s:v>
-      </s:c>
+      <s:c r="E19" s="13"/>
       <s:c r="F19" s="14" t="n">
         <s:v>765.7</s:v>
       </s:c>
@@ -1907,9 +1871,7 @@
       <s:c r="D20" s="12" t="n">
         <s:v>28712.2</s:v>
       </s:c>
-      <s:c r="E20" s="13" t="n">
-        <s:v>8328.99</s:v>
-      </s:c>
+      <s:c r="E20" s="13"/>
       <s:c r="F20" s="14" t="n">
         <s:v>750.1</s:v>
       </s:c>
@@ -1935,9 +1897,7 @@
       <s:c r="D21" s="12" t="n">
         <s:v>28615.2</s:v>
       </s:c>
-      <s:c r="E21" s="13" t="n">
-        <s:v>8325.87</s:v>
-      </s:c>
+      <s:c r="E21" s="13"/>
       <s:c r="F21" s="14" t="n">
         <s:v>723.6</s:v>
       </s:c>
@@ -1963,9 +1923,7 @@
       <s:c r="D22" s="12" t="n">
         <s:v>29216.1</s:v>
       </s:c>
-      <s:c r="E22" s="13" t="n">
-        <s:v>8328.44</s:v>
-      </s:c>
+      <s:c r="E22" s="13"/>
       <s:c r="F22" s="14" t="n">
         <s:v>721.1</s:v>
       </s:c>
@@ -1991,9 +1949,7 @@
       <s:c r="D23" s="12" t="n">
         <s:v>29563</s:v>
       </s:c>
-      <s:c r="E23" s="13" t="n">
-        <s:v>8333.4</s:v>
-      </s:c>
+      <s:c r="E23" s="13"/>
       <s:c r="F23" s="14" t="n">
         <s:v>729.7</s:v>
       </s:c>
@@ -2019,9 +1975,7 @@
       <s:c r="D24" s="12" t="n">
         <s:v>29764</s:v>
       </s:c>
-      <s:c r="E24" s="13" t="n">
-        <s:v>8340.29</s:v>
-      </s:c>
+      <s:c r="E24" s="13"/>
       <s:c r="F24" s="14" t="n">
         <s:v>755</s:v>
       </s:c>
@@ -2047,9 +2001,7 @@
       <s:c r="D25" s="12" t="n">
         <s:v>29725.2</s:v>
       </s:c>
-      <s:c r="E25" s="13" t="n">
-        <s:v>8343.84</s:v>
-      </s:c>
+      <s:c r="E25" s="13"/>
       <s:c r="F25" s="14" t="n">
         <s:v>808.8</s:v>
       </s:c>
@@ -2075,9 +2027,7 @@
       <s:c r="D26" s="12" t="n">
         <s:v>30090.2</s:v>
       </s:c>
-      <s:c r="E26" s="13" t="n">
-        <s:v>8119.43</s:v>
-      </s:c>
+      <s:c r="E26" s="13"/>
       <s:c r="F26" s="14" t="n">
         <s:v>1073</s:v>
       </s:c>
@@ -2103,9 +2053,7 @@
       <s:c r="D27" s="12" t="n">
         <s:v>30086.7</s:v>
       </s:c>
-      <s:c r="E27" s="13" t="n">
-        <s:v>7687.47</s:v>
-      </s:c>
+      <s:c r="E27" s="13"/>
       <s:c r="F27" s="14" t="n">
         <s:v>1546.6</s:v>
       </s:c>
@@ -2131,9 +2079,7 @@
       <s:c r="D28" s="12" t="n">
         <s:v>29857.6</s:v>
       </s:c>
-      <s:c r="E28" s="13" t="n">
-        <s:v>7004.51</s:v>
-      </s:c>
+      <s:c r="E28" s="13"/>
       <s:c r="F28" s="14" t="n">
         <s:v>2180</s:v>
       </s:c>
@@ -2159,9 +2105,7 @@
       <s:c r="D29" s="12" t="n">
         <s:v>29217.4</s:v>
       </s:c>
-      <s:c r="E29" s="13" t="n">
-        <s:v>6334.58</s:v>
-      </s:c>
+      <s:c r="E29" s="13"/>
       <s:c r="F29" s="14" t="n">
         <s:v>2896.7</s:v>
       </s:c>
@@ -2187,9 +2131,7 @@
       <s:c r="D30" s="12" t="n">
         <s:v>28911.7</s:v>
       </s:c>
-      <s:c r="E30" s="13" t="n">
-        <s:v>5869.85</s:v>
-      </s:c>
+      <s:c r="E30" s="13"/>
       <s:c r="F30" s="14" t="n">
         <s:v>3732.4</s:v>
       </s:c>
@@ -2215,9 +2157,7 @@
       <s:c r="D31" s="12" t="n">
         <s:v>28534.5</s:v>
       </s:c>
-      <s:c r="E31" s="13" t="n">
-        <s:v>5390.38</s:v>
-      </s:c>
+      <s:c r="E31" s="13"/>
       <s:c r="F31" s="14" t="n">
         <s:v>4598.2</s:v>
       </s:c>
@@ -2243,9 +2183,7 @@
       <s:c r="D32" s="12" t="n">
         <s:v>28003.8</s:v>
       </s:c>
-      <s:c r="E32" s="13" t="n">
-        <s:v>4927.19</s:v>
-      </s:c>
+      <s:c r="E32" s="13"/>
       <s:c r="F32" s="14" t="n">
         <s:v>5193.9</s:v>
       </s:c>
@@ -2271,9 +2209,7 @@
       <s:c r="D33" s="12" t="n">
         <s:v>27987</s:v>
       </s:c>
-      <s:c r="E33" s="13" t="n">
-        <s:v>4511.83</s:v>
-      </s:c>
+      <s:c r="E33" s="13"/>
       <s:c r="F33" s="14" t="n">
         <s:v>6053.1</s:v>
       </s:c>
@@ -2299,9 +2235,7 @@
       <s:c r="D34" s="12" t="n">
         <s:v>28006.9</s:v>
       </s:c>
-      <s:c r="E34" s="13" t="n">
-        <s:v>4165.79</s:v>
-      </s:c>
+      <s:c r="E34" s="13"/>
       <s:c r="F34" s="14" t="n">
         <s:v>6476.5</s:v>
       </s:c>
@@ -2327,9 +2261,7 @@
       <s:c r="D35" s="12" t="n">
         <s:v>28293.3</s:v>
       </s:c>
-      <s:c r="E35" s="13" t="n">
-        <s:v>4113.66</s:v>
-      </s:c>
+      <s:c r="E35" s="13"/>
       <s:c r="F35" s="14" t="n">
         <s:v>6814.5</s:v>
       </s:c>
@@ -2355,9 +2287,7 @@
       <s:c r="D36" s="12" t="n">
         <s:v>27980.1</s:v>
       </s:c>
-      <s:c r="E36" s="13" t="n">
-        <s:v>4143.71</s:v>
-      </s:c>
+      <s:c r="E36" s="13"/>
       <s:c r="F36" s="14" t="n">
         <s:v>7480</s:v>
       </s:c>
@@ -2383,9 +2313,7 @@
       <s:c r="D37" s="12" t="n">
         <s:v>27844.2</s:v>
       </s:c>
-      <s:c r="E37" s="13" t="n">
-        <s:v>4170.04</s:v>
-      </s:c>
+      <s:c r="E37" s="13"/>
       <s:c r="F37" s="14" t="n">
         <s:v>7817.3</s:v>
       </s:c>
@@ -2411,9 +2339,7 @@
       <s:c r="D38" s="12" t="n">
         <s:v>27717.4</s:v>
       </s:c>
-      <s:c r="E38" s="13" t="n">
-        <s:v>4194.23</s:v>
-      </s:c>
+      <s:c r="E38" s="13"/>
       <s:c r="F38" s="14" t="n">
         <s:v>7808.3</s:v>
       </s:c>
@@ -2439,9 +2365,7 @@
       <s:c r="D39" s="12" t="n">
         <s:v>27545.9</s:v>
       </s:c>
-      <s:c r="E39" s="13" t="n">
-        <s:v>4235.89</s:v>
-      </s:c>
+      <s:c r="E39" s="13"/>
       <s:c r="F39" s="14" t="n">
         <s:v>8663.8</s:v>
       </s:c>
@@ -2467,9 +2391,7 @@
       <s:c r="D40" s="12" t="n">
         <s:v>27181.5</s:v>
       </s:c>
-      <s:c r="E40" s="13" t="n">
-        <s:v>4263.49</s:v>
-      </s:c>
+      <s:c r="E40" s="13"/>
       <s:c r="F40" s="14" t="n">
         <s:v>9366</s:v>
       </s:c>
@@ -2495,9 +2417,7 @@
       <s:c r="D41" s="12" t="n">
         <s:v>26877.9</s:v>
       </s:c>
-      <s:c r="E41" s="13" t="n">
-        <s:v>4284.98</s:v>
-      </s:c>
+      <s:c r="E41" s="13"/>
       <s:c r="F41" s="14" t="n">
         <s:v>9965.4</s:v>
       </s:c>
@@ -2523,9 +2443,7 @@
       <s:c r="D42" s="12" t="n">
         <s:v>26867.3</s:v>
       </s:c>
-      <s:c r="E42" s="13" t="n">
-        <s:v>4314.45</s:v>
-      </s:c>
+      <s:c r="E42" s="13"/>
       <s:c r="F42" s="14" t="n">
         <s:v>10188.9</s:v>
       </s:c>
@@ -2551,9 +2469,7 @@
       <s:c r="D43" s="12" t="n">
         <s:v>26839.7</s:v>
       </s:c>
-      <s:c r="E43" s="13" t="n">
-        <s:v>4333.82</s:v>
-      </s:c>
+      <s:c r="E43" s="13"/>
       <s:c r="F43" s="14" t="n">
         <s:v>10447.3</s:v>
       </s:c>
@@ -2579,9 +2495,7 @@
       <s:c r="D44" s="12" t="n">
         <s:v>26940.6</s:v>
       </s:c>
-      <s:c r="E44" s="13" t="n">
-        <s:v>4353.22</s:v>
-      </s:c>
+      <s:c r="E44" s="13"/>
       <s:c r="F44" s="14" t="n">
         <s:v>10805.8</s:v>
       </s:c>
@@ -2607,9 +2521,7 @@
       <s:c r="D45" s="12" t="n">
         <s:v>26860.3</s:v>
       </s:c>
-      <s:c r="E45" s="13" t="n">
-        <s:v>4371.42</s:v>
-      </s:c>
+      <s:c r="E45" s="13"/>
       <s:c r="F45" s="14" t="n">
         <s:v>10942.7</s:v>
       </s:c>
@@ -2635,9 +2547,7 @@
       <s:c r="D46" s="12" t="n">
         <s:v>28713.6</s:v>
       </s:c>
-      <s:c r="E46" s="13" t="n">
-        <s:v>4368.44</s:v>
-      </s:c>
+      <s:c r="E46" s="13"/>
       <s:c r="F46" s="14" t="n">
         <s:v>11393.3</s:v>
       </s:c>
@@ -2663,9 +2573,7 @@
       <s:c r="D47" s="12" t="n">
         <s:v>28442.3</s:v>
       </s:c>
-      <s:c r="E47" s="13" t="n">
-        <s:v>4392.43</s:v>
-      </s:c>
+      <s:c r="E47" s="13"/>
       <s:c r="F47" s="14" t="n">
         <s:v>11956.9</s:v>
       </s:c>
@@ -2691,9 +2599,7 @@
       <s:c r="D48" s="12" t="n">
         <s:v>27473</s:v>
       </s:c>
-      <s:c r="E48" s="13" t="n">
-        <s:v>4391.37</s:v>
-      </s:c>
+      <s:c r="E48" s="13"/>
       <s:c r="F48" s="14" t="n">
         <s:v>12191.3</s:v>
       </s:c>
@@ -2719,9 +2625,7 @@
       <s:c r="D49" s="12" t="n">
         <s:v>25940.5</s:v>
       </s:c>
-      <s:c r="E49" s="13" t="n">
-        <s:v>4390.9</s:v>
-      </s:c>
+      <s:c r="E49" s="13"/>
       <s:c r="F49" s="14" t="n">
         <s:v>12195.3</s:v>
       </s:c>
@@ -2747,9 +2651,7 @@
       <s:c r="D50" s="12" t="n">
         <s:v>25884.6</s:v>
       </s:c>
-      <s:c r="E50" s="13" t="n">
-        <s:v>4404.88</s:v>
-      </s:c>
+      <s:c r="E50" s="13"/>
       <s:c r="F50" s="14" t="n">
         <s:v>12174.1</s:v>
       </s:c>
@@ -2775,9 +2677,7 @@
       <s:c r="D51" s="12" t="n">
         <s:v>25956.6</s:v>
       </s:c>
-      <s:c r="E51" s="13" t="n">
-        <s:v>4399.19</s:v>
-      </s:c>
+      <s:c r="E51" s="13"/>
       <s:c r="F51" s="14" t="n">
         <s:v>12300.9</s:v>
       </s:c>
@@ -2803,9 +2703,7 @@
       <s:c r="D52" s="12" t="n">
         <s:v>25613.1</s:v>
       </s:c>
-      <s:c r="E52" s="13" t="n">
-        <s:v>4412.46</s:v>
-      </s:c>
+      <s:c r="E52" s="13"/>
       <s:c r="F52" s="14" t="n">
         <s:v>12330.3</s:v>
       </s:c>
@@ -2831,9 +2729,7 @@
       <s:c r="D53" s="12" t="n">
         <s:v>25437.3</s:v>
       </s:c>
-      <s:c r="E53" s="13" t="n">
-        <s:v>4407.24</s:v>
-      </s:c>
+      <s:c r="E53" s="13"/>
       <s:c r="F53" s="14" t="n">
         <s:v>11831.6</s:v>
       </s:c>
@@ -2859,9 +2755,7 @@
       <s:c r="D54" s="12" t="n">
         <s:v>25982.9</s:v>
       </s:c>
-      <s:c r="E54" s="13" t="n">
-        <s:v>4395.56</s:v>
-      </s:c>
+      <s:c r="E54" s="13"/>
       <s:c r="F54" s="14" t="n">
         <s:v>12029.4</s:v>
       </s:c>
@@ -2887,9 +2781,7 @@
       <s:c r="D55" s="12" t="n">
         <s:v>25893.1</s:v>
       </s:c>
-      <s:c r="E55" s="13" t="n">
-        <s:v>4390.12</s:v>
-      </s:c>
+      <s:c r="E55" s="13"/>
       <s:c r="F55" s="14" t="n">
         <s:v>12220.2</s:v>
       </s:c>
@@ -2915,9 +2807,7 @@
       <s:c r="D56" s="12" t="n">
         <s:v>26347.5</s:v>
       </s:c>
-      <s:c r="E56" s="13" t="n">
-        <s:v>4380.01</s:v>
-      </s:c>
+      <s:c r="E56" s="13"/>
       <s:c r="F56" s="14" t="n">
         <s:v>12019.4</s:v>
       </s:c>
@@ -2943,9 +2833,7 @@
       <s:c r="D57" s="12" t="n">
         <s:v>26461.8</s:v>
       </s:c>
-      <s:c r="E57" s="13" t="n">
-        <s:v>4371.52</s:v>
-      </s:c>
+      <s:c r="E57" s="13"/>
       <s:c r="F57" s="14" t="n">
         <s:v>11598</s:v>
       </s:c>
@@ -2971,9 +2859,7 @@
       <s:c r="D58" s="12" t="n">
         <s:v>27015.5</s:v>
       </s:c>
-      <s:c r="E58" s="13" t="n">
-        <s:v>4355.27</s:v>
-      </s:c>
+      <s:c r="E58" s="13"/>
       <s:c r="F58" s="14" t="n">
         <s:v>11631.5</s:v>
       </s:c>
@@ -2999,9 +2885,7 @@
       <s:c r="D59" s="12" t="n">
         <s:v>27372.6</s:v>
       </s:c>
-      <s:c r="E59" s="13" t="n">
-        <s:v>4344.82</s:v>
-      </s:c>
+      <s:c r="E59" s="13"/>
       <s:c r="F59" s="14" t="n">
         <s:v>11141.7</s:v>
       </s:c>
@@ -3027,9 +2911,7 @@
       <s:c r="D60" s="12" t="n">
         <s:v>27788</s:v>
       </s:c>
-      <s:c r="E60" s="13" t="n">
-        <s:v>4333.14</s:v>
-      </s:c>
+      <s:c r="E60" s="13"/>
       <s:c r="F60" s="14" t="n">
         <s:v>10698.8</s:v>
       </s:c>
@@ -3055,9 +2937,7 @@
       <s:c r="D61" s="12" t="n">
         <s:v>28131.9</s:v>
       </s:c>
-      <s:c r="E61" s="13" t="n">
-        <s:v>4310.95</s:v>
-      </s:c>
+      <s:c r="E61" s="13"/>
       <s:c r="F61" s="14" t="n">
         <s:v>10136.5</s:v>
       </s:c>
@@ -3083,9 +2963,7 @@
       <s:c r="D62" s="12" t="n">
         <s:v>28341.8</s:v>
       </s:c>
-      <s:c r="E62" s="13" t="n">
-        <s:v>4420</s:v>
-      </s:c>
+      <s:c r="E62" s="13"/>
       <s:c r="F62" s="14" t="n">
         <s:v>9633.7</s:v>
       </s:c>
@@ -3111,9 +2989,7 @@
       <s:c r="D63" s="12" t="n">
         <s:v>29270.6</s:v>
       </s:c>
-      <s:c r="E63" s="13" t="n">
-        <s:v>4837.65</s:v>
-      </s:c>
+      <s:c r="E63" s="13"/>
       <s:c r="F63" s="14" t="n">
         <s:v>8593.7</s:v>
       </s:c>
@@ -3139,9 +3015,7 @@
       <s:c r="D64" s="12" t="n">
         <s:v>30055.3</s:v>
       </s:c>
-      <s:c r="E64" s="13" t="n">
-        <s:v>5295.01</s:v>
-      </s:c>
+      <s:c r="E64" s="13"/>
       <s:c r="F64" s="14" t="n">
         <s:v>7979.3</s:v>
       </s:c>
@@ -3167,9 +3041,7 @@
       <s:c r="D65" s="12" t="n">
         <s:v>30583.7</s:v>
       </s:c>
-      <s:c r="E65" s="13" t="n">
-        <s:v>6000.27</s:v>
-      </s:c>
+      <s:c r="E65" s="13"/>
       <s:c r="F65" s="14" t="n">
         <s:v>7344</s:v>
       </s:c>
@@ -3195,9 +3067,7 @@
       <s:c r="D66" s="12" t="n">
         <s:v>31672.1</s:v>
       </s:c>
-      <s:c r="E66" s="13" t="n">
-        <s:v>6700.94</s:v>
-      </s:c>
+      <s:c r="E66" s="13"/>
       <s:c r="F66" s="14" t="n">
         <s:v>6221.2</s:v>
       </s:c>
@@ -3223,9 +3093,7 @@
       <s:c r="D67" s="12" t="n">
         <s:v>32459.7</s:v>
       </s:c>
-      <s:c r="E67" s="13" t="n">
-        <s:v>7202.32</s:v>
-      </s:c>
+      <s:c r="E67" s="13"/>
       <s:c r="F67" s="14" t="n">
         <s:v>5587.1</s:v>
       </s:c>
@@ -3251,9 +3119,7 @@
       <s:c r="D68" s="12" t="n">
         <s:v>33425.8</s:v>
       </s:c>
-      <s:c r="E68" s="13" t="n">
-        <s:v>7681.91</s:v>
-      </s:c>
+      <s:c r="E68" s="13"/>
       <s:c r="F68" s="14" t="n">
         <s:v>4872.9</s:v>
       </s:c>
@@ -3279,9 +3145,7 @@
       <s:c r="D69" s="12" t="n">
         <s:v>34781.3</s:v>
       </s:c>
-      <s:c r="E69" s="13" t="n">
-        <s:v>8198.39</s:v>
-      </s:c>
+      <s:c r="E69" s="13"/>
       <s:c r="F69" s="14" t="n">
         <s:v>3958.2</s:v>
       </s:c>
@@ -3307,9 +3171,7 @@
       <s:c r="D70" s="12" t="n">
         <s:v>35930.5</s:v>
       </s:c>
-      <s:c r="E70" s="13" t="n">
-        <s:v>8662.6</s:v>
-      </s:c>
+      <s:c r="E70" s="13"/>
       <s:c r="F70" s="14" t="n">
         <s:v>3213.6</s:v>
       </s:c>
@@ -3335,9 +3197,7 @@
       <s:c r="D71" s="12" t="n">
         <s:v>36662.2</s:v>
       </s:c>
-      <s:c r="E71" s="13" t="n">
-        <s:v>8797.23</s:v>
-      </s:c>
+      <s:c r="E71" s="13"/>
       <s:c r="F71" s="14" t="n">
         <s:v>2495.8</s:v>
       </s:c>
@@ -3363,9 +3223,7 @@
       <s:c r="D72" s="12" t="n">
         <s:v>37310.9</s:v>
       </s:c>
-      <s:c r="E72" s="13" t="n">
-        <s:v>8812.05</s:v>
-      </s:c>
+      <s:c r="E72" s="13"/>
       <s:c r="F72" s="14" t="n">
         <s:v>1830.8</s:v>
       </s:c>
@@ -3391,9 +3249,7 @@
       <s:c r="D73" s="12" t="n">
         <s:v>37248</s:v>
       </s:c>
-      <s:c r="E73" s="13" t="n">
-        <s:v>8828.74</s:v>
-      </s:c>
+      <s:c r="E73" s="13"/>
       <s:c r="F73" s="14" t="n">
         <s:v>1296</s:v>
       </s:c>
@@ -3419,9 +3275,7 @@
       <s:c r="D74" s="12" t="n">
         <s:v>37578.5</s:v>
       </s:c>
-      <s:c r="E74" s="13" t="n">
-        <s:v>8857.03</s:v>
-      </s:c>
+      <s:c r="E74" s="13"/>
       <s:c r="F74" s="14" t="n">
         <s:v>964.3</s:v>
       </s:c>
@@ -3447,9 +3301,7 @@
       <s:c r="D75" s="12" t="n">
         <s:v>37357</s:v>
       </s:c>
-      <s:c r="E75" s="13" t="n">
-        <s:v>8888.76</s:v>
-      </s:c>
+      <s:c r="E75" s="13"/>
       <s:c r="F75" s="14" t="n">
         <s:v>766.7</s:v>
       </s:c>
@@ -3475,9 +3327,7 @@
       <s:c r="D76" s="12" t="n">
         <s:v>36822.9</s:v>
       </s:c>
-      <s:c r="E76" s="13" t="n">
-        <s:v>8877.33</s:v>
-      </s:c>
+      <s:c r="E76" s="13"/>
       <s:c r="F76" s="14" t="n">
         <s:v>615.6</s:v>
       </s:c>
@@ -3503,9 +3353,7 @@
       <s:c r="D77" s="12" t="n">
         <s:v>37335.2</s:v>
       </s:c>
-      <s:c r="E77" s="13" t="n">
-        <s:v>8870.4</s:v>
-      </s:c>
+      <s:c r="E77" s="13"/>
       <s:c r="F77" s="14" t="n">
         <s:v>646.1</s:v>
       </s:c>
@@ -3531,9 +3379,7 @@
       <s:c r="D78" s="12" t="n">
         <s:v>36841.6</s:v>
       </s:c>
-      <s:c r="E78" s="13" t="n">
-        <s:v>8866.05</s:v>
-      </s:c>
+      <s:c r="E78" s="13"/>
       <s:c r="F78" s="14" t="n">
         <s:v>688.4</s:v>
       </s:c>
@@ -3559,9 +3405,7 @@
       <s:c r="D79" s="12" t="n">
         <s:v>36272.1</s:v>
       </s:c>
-      <s:c r="E79" s="13" t="n">
-        <s:v>8867.44</s:v>
-      </s:c>
+      <s:c r="E79" s="13"/>
       <s:c r="F79" s="14" t="n">
         <s:v>727.7</s:v>
       </s:c>
@@ -3587,9 +3431,7 @@
       <s:c r="D80" s="12" t="n">
         <s:v>36075.1</s:v>
       </s:c>
-      <s:c r="E80" s="13" t="n">
-        <s:v>8872.02</s:v>
-      </s:c>
+      <s:c r="E80" s="13"/>
       <s:c r="F80" s="14" t="n">
         <s:v>781.1</s:v>
       </s:c>
@@ -3615,9 +3457,7 @@
       <s:c r="D81" s="12" t="n">
         <s:v>35606.8</s:v>
       </s:c>
-      <s:c r="E81" s="13" t="n">
-        <s:v>8878.81</s:v>
-      </s:c>
+      <s:c r="E81" s="13"/>
       <s:c r="F81" s="14" t="n">
         <s:v>813.1</s:v>
       </s:c>
@@ -3643,9 +3483,7 @@
       <s:c r="D82" s="12" t="n">
         <s:v>35014.9</s:v>
       </s:c>
-      <s:c r="E82" s="13" t="n">
-        <s:v>8875.88</s:v>
-      </s:c>
+      <s:c r="E82" s="13"/>
       <s:c r="F82" s="14" t="n">
         <s:v>890.1</s:v>
       </s:c>
@@ -3671,9 +3509,7 @@
       <s:c r="D83" s="12" t="n">
         <s:v>34671.3</s:v>
       </s:c>
-      <s:c r="E83" s="13" t="n">
-        <s:v>8874.76</s:v>
-      </s:c>
+      <s:c r="E83" s="13"/>
       <s:c r="F83" s="14" t="n">
         <s:v>905.7</s:v>
       </s:c>
@@ -3699,9 +3535,7 @@
       <s:c r="D84" s="12" t="n">
         <s:v>34660.2</s:v>
       </s:c>
-      <s:c r="E84" s="13" t="n">
-        <s:v>8876.79</s:v>
-      </s:c>
+      <s:c r="E84" s="13"/>
       <s:c r="F84" s="14" t="n">
         <s:v>957.6</s:v>
       </s:c>
@@ -3727,9 +3561,7 @@
       <s:c r="D85" s="12" t="n">
         <s:v>34285.2</s:v>
       </s:c>
-      <s:c r="E85" s="13" t="n">
-        <s:v>8875.77</s:v>
-      </s:c>
+      <s:c r="E85" s="13"/>
       <s:c r="F85" s="14" t="n">
         <s:v>988.3</s:v>
       </s:c>
@@ -3755,9 +3587,7 @@
       <s:c r="D86" s="12" t="n">
         <s:v>33958.5</s:v>
       </s:c>
-      <s:c r="E86" s="13" t="n">
-        <s:v>8859.9</s:v>
-      </s:c>
+      <s:c r="E86" s="13"/>
       <s:c r="F86" s="14" t="n">
         <s:v>1043.1</s:v>
       </s:c>
@@ -3783,9 +3613,7 @@
       <s:c r="D87" s="12" t="n">
         <s:v>33657</s:v>
       </s:c>
-      <s:c r="E87" s="13" t="n">
-        <s:v>8859.27</s:v>
-      </s:c>
+      <s:c r="E87" s="13"/>
       <s:c r="F87" s="14" t="n">
         <s:v>1066.9</s:v>
       </s:c>
@@ -3811,9 +3639,7 @@
       <s:c r="D88" s="12" t="n">
         <s:v>33385.9</s:v>
       </s:c>
-      <s:c r="E88" s="13" t="n">
-        <s:v>8856.46</s:v>
-      </s:c>
+      <s:c r="E88" s="13"/>
       <s:c r="F88" s="14" t="n">
         <s:v>1044.6</s:v>
       </s:c>
@@ -3839,9 +3665,7 @@
       <s:c r="D89" s="12" t="n">
         <s:v>33043.4</s:v>
       </s:c>
-      <s:c r="E89" s="13" t="n">
-        <s:v>8854.96</s:v>
-      </s:c>
+      <s:c r="E89" s="13"/>
       <s:c r="F89" s="14" t="n">
         <s:v>984.4</s:v>
       </s:c>
@@ -3867,9 +3691,7 @@
       <s:c r="D90" s="12" t="n">
         <s:v>32765.2</s:v>
       </s:c>
-      <s:c r="E90" s="13" t="n">
-        <s:v>8803.33</s:v>
-      </s:c>
+      <s:c r="E90" s="13"/>
       <s:c r="F90" s="14" t="n">
         <s:v>938.2</s:v>
       </s:c>
@@ -3895,9 +3717,7 @@
       <s:c r="D91" s="12" t="n">
         <s:v>32586.9</s:v>
       </s:c>
-      <s:c r="E91" s="13" t="n">
-        <s:v>8803.3</s:v>
-      </s:c>
+      <s:c r="E91" s="13"/>
       <s:c r="F91" s="14" t="n">
         <s:v>897.7</s:v>
       </s:c>
@@ -3923,9 +3743,7 @@
       <s:c r="D92" s="12" t="n">
         <s:v>31863.7</s:v>
       </s:c>
-      <s:c r="E92" s="13" t="n">
-        <s:v>8799.05</s:v>
-      </s:c>
+      <s:c r="E92" s="13"/>
       <s:c r="F92" s="14" t="n">
         <s:v>863</s:v>
       </s:c>
@@ -3951,9 +3769,7 @@
       <s:c r="D93" s="12" t="n">
         <s:v>31330.7</s:v>
       </s:c>
-      <s:c r="E93" s="13" t="n">
-        <s:v>8796.74</s:v>
-      </s:c>
+      <s:c r="E93" s="13"/>
       <s:c r="F93" s="14" t="n">
         <s:v>829.6</s:v>
       </s:c>
@@ -3979,9 +3795,7 @@
       <s:c r="D94" s="12" t="n">
         <s:v>30595.8</s:v>
       </s:c>
-      <s:c r="E94" s="13" t="n">
-        <s:v>8797.29</s:v>
-      </s:c>
+      <s:c r="E94" s="13"/>
       <s:c r="F94" s="14" t="n">
         <s:v>828.4</s:v>
       </s:c>
@@ -4007,9 +3821,7 @@
       <s:c r="D95" s="12" t="n">
         <s:v>30061.5</s:v>
       </s:c>
-      <s:c r="E95" s="13" t="n">
-        <s:v>8795.57</s:v>
-      </s:c>
+      <s:c r="E95" s="13"/>
       <s:c r="F95" s="14" t="n">
         <s:v>831</s:v>
       </s:c>
@@ -4035,9 +3847,7 @@
       <s:c r="D96" s="12" t="n">
         <s:v>29568.1</s:v>
       </s:c>
-      <s:c r="E96" s="13" t="n">
-        <s:v>8791.44</s:v>
-      </s:c>
+      <s:c r="E96" s="13"/>
       <s:c r="F96" s="14" t="n">
         <s:v>845.9</s:v>
       </s:c>
@@ -4065,9 +3875,7 @@
       <s:c r="D97" s="12" t="n">
         <s:v>29535.8</s:v>
       </s:c>
-      <s:c r="E97" s="13" t="n">
-        <s:v>8791.87</s:v>
-      </s:c>
+      <s:c r="E97" s="13"/>
       <s:c r="F97" s="14" t="n">
         <s:v>857.2</s:v>
       </s:c>

--- a/review-results/河北实时运行及市场出清数据-20260904.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260904.xlsx
@@ -1403,7 +1403,9 @@
       <s:c r="D2" s="12" t="n">
         <s:v>29688.4</s:v>
       </s:c>
-      <s:c r="E2" s="13"/>
+      <s:c r="E2" s="13" t="n">
+        <s:v>8424.55</s:v>
+      </s:c>
       <s:c r="F2" s="14" t="n">
         <s:v>1099.4</s:v>
       </s:c>
@@ -1429,7 +1431,9 @@
       <s:c r="D3" s="12" t="n">
         <s:v>29374.4</s:v>
       </s:c>
-      <s:c r="E3" s="13"/>
+      <s:c r="E3" s="13" t="n">
+        <s:v>8416.93</s:v>
+      </s:c>
       <s:c r="F3" s="14" t="n">
         <s:v>1102.9</s:v>
       </s:c>
@@ -1455,7 +1459,9 @@
       <s:c r="D4" s="12" t="n">
         <s:v>29136.7</s:v>
       </s:c>
-      <s:c r="E4" s="13"/>
+      <s:c r="E4" s="13" t="n">
+        <s:v>8408.02</s:v>
+      </s:c>
       <s:c r="F4" s="14" t="n">
         <s:v>1112.6</s:v>
       </s:c>
@@ -1481,7 +1487,9 @@
       <s:c r="D5" s="12" t="n">
         <s:v>29083.2</s:v>
       </s:c>
-      <s:c r="E5" s="13"/>
+      <s:c r="E5" s="13" t="n">
+        <s:v>8397.79</s:v>
+      </s:c>
       <s:c r="F5" s="14" t="n">
         <s:v>1048.3</s:v>
       </s:c>
@@ -1507,7 +1515,9 @@
       <s:c r="D6" s="12" t="n">
         <s:v>28945.2</s:v>
       </s:c>
-      <s:c r="E6" s="13"/>
+      <s:c r="E6" s="13" t="n">
+        <s:v>8388.36</s:v>
+      </s:c>
       <s:c r="F6" s="14" t="n">
         <s:v>1014.8</s:v>
       </s:c>
@@ -1533,7 +1543,9 @@
       <s:c r="D7" s="12" t="n">
         <s:v>28797.6</s:v>
       </s:c>
-      <s:c r="E7" s="13"/>
+      <s:c r="E7" s="13" t="n">
+        <s:v>8382.89</s:v>
+      </s:c>
       <s:c r="F7" s="14" t="n">
         <s:v>967.5</s:v>
       </s:c>
@@ -1559,7 +1571,9 @@
       <s:c r="D8" s="12" t="n">
         <s:v>28523.7</s:v>
       </s:c>
-      <s:c r="E8" s="13"/>
+      <s:c r="E8" s="13" t="n">
+        <s:v>8377.1</s:v>
+      </s:c>
       <s:c r="F8" s="14" t="n">
         <s:v>927.6</s:v>
       </s:c>
@@ -1585,7 +1599,9 @@
       <s:c r="D9" s="12" t="n">
         <s:v>28777.8</s:v>
       </s:c>
-      <s:c r="E9" s="13"/>
+      <s:c r="E9" s="13" t="n">
+        <s:v>8371.96</s:v>
+      </s:c>
       <s:c r="F9" s="14" t="n">
         <s:v>864.4</s:v>
       </s:c>
@@ -1611,7 +1627,9 @@
       <s:c r="D10" s="12" t="n">
         <s:v>31474.5</s:v>
       </s:c>
-      <s:c r="E10" s="13"/>
+      <s:c r="E10" s="13" t="n">
+        <s:v>8363.99</s:v>
+      </s:c>
       <s:c r="F10" s="14" t="n">
         <s:v>831.6</s:v>
       </s:c>
@@ -1637,7 +1655,9 @@
       <s:c r="D11" s="12" t="n">
         <s:v>31312.5</s:v>
       </s:c>
-      <s:c r="E11" s="13"/>
+      <s:c r="E11" s="13" t="n">
+        <s:v>8356.4</s:v>
+      </s:c>
       <s:c r="F11" s="14" t="n">
         <s:v>823.6</s:v>
       </s:c>
@@ -1663,7 +1683,9 @@
       <s:c r="D12" s="12" t="n">
         <s:v>30712.6</s:v>
       </s:c>
-      <s:c r="E12" s="13"/>
+      <s:c r="E12" s="13" t="n">
+        <s:v>8349.51</s:v>
+      </s:c>
       <s:c r="F12" s="14" t="n">
         <s:v>816.9</s:v>
       </s:c>
@@ -1689,7 +1711,9 @@
       <s:c r="D13" s="12" t="n">
         <s:v>29991.9</s:v>
       </s:c>
-      <s:c r="E13" s="13"/>
+      <s:c r="E13" s="13" t="n">
+        <s:v>8343.21</s:v>
+      </s:c>
       <s:c r="F13" s="14" t="n">
         <s:v>804.3</s:v>
       </s:c>
@@ -1715,7 +1739,9 @@
       <s:c r="D14" s="12" t="n">
         <s:v>29579.1</s:v>
       </s:c>
-      <s:c r="E14" s="13"/>
+      <s:c r="E14" s="13" t="n">
+        <s:v>8339.18</s:v>
+      </s:c>
       <s:c r="F14" s="14" t="n">
         <s:v>793.3</s:v>
       </s:c>
@@ -1741,7 +1767,9 @@
       <s:c r="D15" s="12" t="n">
         <s:v>29369</s:v>
       </s:c>
-      <s:c r="E15" s="13"/>
+      <s:c r="E15" s="13" t="n">
+        <s:v>8334.05</s:v>
+      </s:c>
       <s:c r="F15" s="14" t="n">
         <s:v>780.1</s:v>
       </s:c>
@@ -1767,7 +1795,9 @@
       <s:c r="D16" s="12" t="n">
         <s:v>29180.9</s:v>
       </s:c>
-      <s:c r="E16" s="13"/>
+      <s:c r="E16" s="13" t="n">
+        <s:v>8329.36</s:v>
+      </s:c>
       <s:c r="F16" s="14" t="n">
         <s:v>772.3</s:v>
       </s:c>
@@ -1793,7 +1823,9 @@
       <s:c r="D17" s="12" t="n">
         <s:v>28947.5</s:v>
       </s:c>
-      <s:c r="E17" s="13"/>
+      <s:c r="E17" s="13" t="n">
+        <s:v>8325.75</s:v>
+      </s:c>
       <s:c r="F17" s="14" t="n">
         <s:v>759.1</s:v>
       </s:c>
@@ -1819,7 +1851,9 @@
       <s:c r="D18" s="12" t="n">
         <s:v>28671.8</s:v>
       </s:c>
-      <s:c r="E18" s="13"/>
+      <s:c r="E18" s="13" t="n">
+        <s:v>8333.85</s:v>
+      </s:c>
       <s:c r="F18" s="14" t="n">
         <s:v>756.9</s:v>
       </s:c>
@@ -1845,7 +1879,9 @@
       <s:c r="D19" s="12" t="n">
         <s:v>28547.2</s:v>
       </s:c>
-      <s:c r="E19" s="13"/>
+      <s:c r="E19" s="13" t="n">
+        <s:v>8331.05</s:v>
+      </s:c>
       <s:c r="F19" s="14" t="n">
         <s:v>765.7</s:v>
       </s:c>
@@ -1871,7 +1907,9 @@
       <s:c r="D20" s="12" t="n">
         <s:v>28712.2</s:v>
       </s:c>
-      <s:c r="E20" s="13"/>
+      <s:c r="E20" s="13" t="n">
+        <s:v>8328.99</s:v>
+      </s:c>
       <s:c r="F20" s="14" t="n">
         <s:v>750.1</s:v>
       </s:c>
@@ -1897,7 +1935,9 @@
       <s:c r="D21" s="12" t="n">
         <s:v>28615.2</s:v>
       </s:c>
-      <s:c r="E21" s="13"/>
+      <s:c r="E21" s="13" t="n">
+        <s:v>8325.87</s:v>
+      </s:c>
       <s:c r="F21" s="14" t="n">
         <s:v>723.6</s:v>
       </s:c>
@@ -1923,7 +1963,9 @@
       <s:c r="D22" s="12" t="n">
         <s:v>29216.1</s:v>
       </s:c>
-      <s:c r="E22" s="13"/>
+      <s:c r="E22" s="13" t="n">
+        <s:v>8328.44</s:v>
+      </s:c>
       <s:c r="F22" s="14" t="n">
         <s:v>721.1</s:v>
       </s:c>
@@ -1949,7 +1991,9 @@
       <s:c r="D23" s="12" t="n">
         <s:v>29563</s:v>
       </s:c>
-      <s:c r="E23" s="13"/>
+      <s:c r="E23" s="13" t="n">
+        <s:v>8333.4</s:v>
+      </s:c>
       <s:c r="F23" s="14" t="n">
         <s:v>729.7</s:v>
       </s:c>
@@ -1975,7 +2019,9 @@
       <s:c r="D24" s="12" t="n">
         <s:v>29764</s:v>
       </s:c>
-      <s:c r="E24" s="13"/>
+      <s:c r="E24" s="13" t="n">
+        <s:v>8340.29</s:v>
+      </s:c>
       <s:c r="F24" s="14" t="n">
         <s:v>755</s:v>
       </s:c>
@@ -2001,7 +2047,9 @@
       <s:c r="D25" s="12" t="n">
         <s:v>29725.2</s:v>
       </s:c>
-      <s:c r="E25" s="13"/>
+      <s:c r="E25" s="13" t="n">
+        <s:v>8343.84</s:v>
+      </s:c>
       <s:c r="F25" s="14" t="n">
         <s:v>808.8</s:v>
       </s:c>
@@ -2027,7 +2075,9 @@
       <s:c r="D26" s="12" t="n">
         <s:v>30090.2</s:v>
       </s:c>
-      <s:c r="E26" s="13"/>
+      <s:c r="E26" s="13" t="n">
+        <s:v>8119.43</s:v>
+      </s:c>
       <s:c r="F26" s="14" t="n">
         <s:v>1073</s:v>
       </s:c>
@@ -2053,7 +2103,9 @@
       <s:c r="D27" s="12" t="n">
         <s:v>30086.7</s:v>
       </s:c>
-      <s:c r="E27" s="13"/>
+      <s:c r="E27" s="13" t="n">
+        <s:v>7687.47</s:v>
+      </s:c>
       <s:c r="F27" s="14" t="n">
         <s:v>1546.6</s:v>
       </s:c>
@@ -2079,7 +2131,9 @@
       <s:c r="D28" s="12" t="n">
         <s:v>29857.6</s:v>
       </s:c>
-      <s:c r="E28" s="13"/>
+      <s:c r="E28" s="13" t="n">
+        <s:v>7004.51</s:v>
+      </s:c>
       <s:c r="F28" s="14" t="n">
         <s:v>2180</s:v>
       </s:c>
@@ -2105,7 +2159,9 @@
       <s:c r="D29" s="12" t="n">
         <s:v>29217.4</s:v>
       </s:c>
-      <s:c r="E29" s="13"/>
+      <s:c r="E29" s="13" t="n">
+        <s:v>6334.58</s:v>
+      </s:c>
       <s:c r="F29" s="14" t="n">
         <s:v>2896.7</s:v>
       </s:c>
@@ -2131,7 +2187,9 @@
       <s:c r="D30" s="12" t="n">
         <s:v>28911.7</s:v>
       </s:c>
-      <s:c r="E30" s="13"/>
+      <s:c r="E30" s="13" t="n">
+        <s:v>5869.85</s:v>
+      </s:c>
       <s:c r="F30" s="14" t="n">
         <s:v>3732.4</s:v>
       </s:c>
@@ -2157,7 +2215,9 @@
       <s:c r="D31" s="12" t="n">
         <s:v>28534.5</s:v>
       </s:c>
-      <s:c r="E31" s="13"/>
+      <s:c r="E31" s="13" t="n">
+        <s:v>5390.38</s:v>
+      </s:c>
       <s:c r="F31" s="14" t="n">
         <s:v>4598.2</s:v>
       </s:c>
@@ -2183,7 +2243,9 @@
       <s:c r="D32" s="12" t="n">
         <s:v>28003.8</s:v>
       </s:c>
-      <s:c r="E32" s="13"/>
+      <s:c r="E32" s="13" t="n">
+        <s:v>4927.19</s:v>
+      </s:c>
       <s:c r="F32" s="14" t="n">
         <s:v>5193.9</s:v>
       </s:c>
@@ -2209,7 +2271,9 @@
       <s:c r="D33" s="12" t="n">
         <s:v>27987</s:v>
       </s:c>
-      <s:c r="E33" s="13"/>
+      <s:c r="E33" s="13" t="n">
+        <s:v>4511.83</s:v>
+      </s:c>
       <s:c r="F33" s="14" t="n">
         <s:v>6053.1</s:v>
       </s:c>
@@ -2235,7 +2299,9 @@
       <s:c r="D34" s="12" t="n">
         <s:v>28006.9</s:v>
       </s:c>
-      <s:c r="E34" s="13"/>
+      <s:c r="E34" s="13" t="n">
+        <s:v>4165.79</s:v>
+      </s:c>
       <s:c r="F34" s="14" t="n">
         <s:v>6476.5</s:v>
       </s:c>
@@ -2261,7 +2327,9 @@
       <s:c r="D35" s="12" t="n">
         <s:v>28293.3</s:v>
       </s:c>
-      <s:c r="E35" s="13"/>
+      <s:c r="E35" s="13" t="n">
+        <s:v>4113.66</s:v>
+      </s:c>
       <s:c r="F35" s="14" t="n">
         <s:v>6814.5</s:v>
       </s:c>
@@ -2287,7 +2355,9 @@
       <s:c r="D36" s="12" t="n">
         <s:v>27980.1</s:v>
       </s:c>
-      <s:c r="E36" s="13"/>
+      <s:c r="E36" s="13" t="n">
+        <s:v>4143.71</s:v>
+      </s:c>
       <s:c r="F36" s="14" t="n">
         <s:v>7480</s:v>
       </s:c>
@@ -2313,7 +2383,9 @@
       <s:c r="D37" s="12" t="n">
         <s:v>27844.2</s:v>
       </s:c>
-      <s:c r="E37" s="13"/>
+      <s:c r="E37" s="13" t="n">
+        <s:v>4170.04</s:v>
+      </s:c>
       <s:c r="F37" s="14" t="n">
         <s:v>7817.3</s:v>
       </s:c>
@@ -2339,7 +2411,9 @@
       <s:c r="D38" s="12" t="n">
         <s:v>27717.4</s:v>
       </s:c>
-      <s:c r="E38" s="13"/>
+      <s:c r="E38" s="13" t="n">
+        <s:v>4194.23</s:v>
+      </s:c>
       <s:c r="F38" s="14" t="n">
         <s:v>7808.3</s:v>
       </s:c>
@@ -2365,7 +2439,9 @@
       <s:c r="D39" s="12" t="n">
         <s:v>27545.9</s:v>
       </s:c>
-      <s:c r="E39" s="13"/>
+      <s:c r="E39" s="13" t="n">
+        <s:v>4235.89</s:v>
+      </s:c>
       <s:c r="F39" s="14" t="n">
         <s:v>8663.8</s:v>
       </s:c>
@@ -2391,7 +2467,9 @@
       <s:c r="D40" s="12" t="n">
         <s:v>27181.5</s:v>
       </s:c>
-      <s:c r="E40" s="13"/>
+      <s:c r="E40" s="13" t="n">
+        <s:v>4263.49</s:v>
+      </s:c>
       <s:c r="F40" s="14" t="n">
         <s:v>9366</s:v>
       </s:c>
@@ -2417,7 +2495,9 @@
       <s:c r="D41" s="12" t="n">
         <s:v>26877.9</s:v>
       </s:c>
-      <s:c r="E41" s="13"/>
+      <s:c r="E41" s="13" t="n">
+        <s:v>4284.98</s:v>
+      </s:c>
       <s:c r="F41" s="14" t="n">
         <s:v>9965.4</s:v>
       </s:c>
@@ -2443,7 +2523,9 @@
       <s:c r="D42" s="12" t="n">
         <s:v>26867.3</s:v>
       </s:c>
-      <s:c r="E42" s="13"/>
+      <s:c r="E42" s="13" t="n">
+        <s:v>4314.45</s:v>
+      </s:c>
       <s:c r="F42" s="14" t="n">
         <s:v>10188.9</s:v>
       </s:c>
@@ -2469,7 +2551,9 @@
       <s:c r="D43" s="12" t="n">
         <s:v>26839.7</s:v>
       </s:c>
-      <s:c r="E43" s="13"/>
+      <s:c r="E43" s="13" t="n">
+        <s:v>4333.82</s:v>
+      </s:c>
       <s:c r="F43" s="14" t="n">
         <s:v>10447.3</s:v>
       </s:c>
@@ -2495,7 +2579,9 @@
       <s:c r="D44" s="12" t="n">
         <s:v>26940.6</s:v>
       </s:c>
-      <s:c r="E44" s="13"/>
+      <s:c r="E44" s="13" t="n">
+        <s:v>4353.22</s:v>
+      </s:c>
       <s:c r="F44" s="14" t="n">
         <s:v>10805.8</s:v>
       </s:c>
@@ -2521,7 +2607,9 @@
       <s:c r="D45" s="12" t="n">
         <s:v>26860.3</s:v>
       </s:c>
-      <s:c r="E45" s="13"/>
+      <s:c r="E45" s="13" t="n">
+        <s:v>4371.42</s:v>
+      </s:c>
       <s:c r="F45" s="14" t="n">
         <s:v>10942.7</s:v>
       </s:c>
@@ -2547,7 +2635,9 @@
       <s:c r="D46" s="12" t="n">
         <s:v>28713.6</s:v>
       </s:c>
-      <s:c r="E46" s="13"/>
+      <s:c r="E46" s="13" t="n">
+        <s:v>4368.44</s:v>
+      </s:c>
       <s:c r="F46" s="14" t="n">
         <s:v>11393.3</s:v>
       </s:c>
@@ -2573,7 +2663,9 @@
       <s:c r="D47" s="12" t="n">
         <s:v>28442.3</s:v>
       </s:c>
-      <s:c r="E47" s="13"/>
+      <s:c r="E47" s="13" t="n">
+        <s:v>4392.43</s:v>
+      </s:c>
       <s:c r="F47" s="14" t="n">
         <s:v>11956.9</s:v>
       </s:c>
@@ -2599,7 +2691,9 @@
       <s:c r="D48" s="12" t="n">
         <s:v>27473</s:v>
       </s:c>
-      <s:c r="E48" s="13"/>
+      <s:c r="E48" s="13" t="n">
+        <s:v>4391.37</s:v>
+      </s:c>
       <s:c r="F48" s="14" t="n">
         <s:v>12191.3</s:v>
       </s:c>
@@ -2625,7 +2719,9 @@
       <s:c r="D49" s="12" t="n">
         <s:v>25940.5</s:v>
       </s:c>
-      <s:c r="E49" s="13"/>
+      <s:c r="E49" s="13" t="n">
+        <s:v>4390.9</s:v>
+      </s:c>
       <s:c r="F49" s="14" t="n">
         <s:v>12195.3</s:v>
       </s:c>
@@ -2651,7 +2747,9 @@
       <s:c r="D50" s="12" t="n">
         <s:v>25884.6</s:v>
       </s:c>
-      <s:c r="E50" s="13"/>
+      <s:c r="E50" s="13" t="n">
+        <s:v>4404.88</s:v>
+      </s:c>
       <s:c r="F50" s="14" t="n">
         <s:v>12174.1</s:v>
       </s:c>
@@ -2677,7 +2775,9 @@
       <s:c r="D51" s="12" t="n">
         <s:v>25956.6</s:v>
       </s:c>
-      <s:c r="E51" s="13"/>
+      <s:c r="E51" s="13" t="n">
+        <s:v>4399.19</s:v>
+      </s:c>
       <s:c r="F51" s="14" t="n">
         <s:v>12300.9</s:v>
       </s:c>
@@ -2703,7 +2803,9 @@
       <s:c r="D52" s="12" t="n">
         <s:v>25613.1</s:v>
       </s:c>
-      <s:c r="E52" s="13"/>
+      <s:c r="E52" s="13" t="n">
+        <s:v>4412.46</s:v>
+      </s:c>
       <s:c r="F52" s="14" t="n">
         <s:v>12330.3</s:v>
       </s:c>
@@ -2729,7 +2831,9 @@
       <s:c r="D53" s="12" t="n">
         <s:v>25437.3</s:v>
       </s:c>
-      <s:c r="E53" s="13"/>
+      <s:c r="E53" s="13" t="n">
+        <s:v>4407.24</s:v>
+      </s:c>
       <s:c r="F53" s="14" t="n">
         <s:v>11831.6</s:v>
       </s:c>
@@ -2755,7 +2859,9 @@
       <s:c r="D54" s="12" t="n">
         <s:v>25982.9</s:v>
       </s:c>
-      <s:c r="E54" s="13"/>
+      <s:c r="E54" s="13" t="n">
+        <s:v>4395.56</s:v>
+      </s:c>
       <s:c r="F54" s="14" t="n">
         <s:v>12029.4</s:v>
       </s:c>
@@ -2781,7 +2887,9 @@
       <s:c r="D55" s="12" t="n">
         <s:v>25893.1</s:v>
       </s:c>
-      <s:c r="E55" s="13"/>
+      <s:c r="E55" s="13" t="n">
+        <s:v>4390.12</s:v>
+      </s:c>
       <s:c r="F55" s="14" t="n">
         <s:v>12220.2</s:v>
       </s:c>
@@ -2807,7 +2915,9 @@
       <s:c r="D56" s="12" t="n">
         <s:v>26347.5</s:v>
       </s:c>
-      <s:c r="E56" s="13"/>
+      <s:c r="E56" s="13" t="n">
+        <s:v>4380.01</s:v>
+      </s:c>
       <s:c r="F56" s="14" t="n">
         <s:v>12019.4</s:v>
       </s:c>
@@ -2833,7 +2943,9 @@
       <s:c r="D57" s="12" t="n">
         <s:v>26461.8</s:v>
       </s:c>
-      <s:c r="E57" s="13"/>
+      <s:c r="E57" s="13" t="n">
+        <s:v>4371.52</s:v>
+      </s:c>
       <s:c r="F57" s="14" t="n">
         <s:v>11598</s:v>
       </s:c>
@@ -2859,7 +2971,9 @@
       <s:c r="D58" s="12" t="n">
         <s:v>27015.5</s:v>
       </s:c>
-      <s:c r="E58" s="13"/>
+      <s:c r="E58" s="13" t="n">
+        <s:v>4355.27</s:v>
+      </s:c>
       <s:c r="F58" s="14" t="n">
         <s:v>11631.5</s:v>
       </s:c>
@@ -2885,7 +2999,9 @@
       <s:c r="D59" s="12" t="n">
         <s:v>27372.6</s:v>
       </s:c>
-      <s:c r="E59" s="13"/>
+      <s:c r="E59" s="13" t="n">
+        <s:v>4344.82</s:v>
+      </s:c>
       <s:c r="F59" s="14" t="n">
         <s:v>11141.7</s:v>
       </s:c>
@@ -2911,7 +3027,9 @@
       <s:c r="D60" s="12" t="n">
         <s:v>27788</s:v>
       </s:c>
-      <s:c r="E60" s="13"/>
+      <s:c r="E60" s="13" t="n">
+        <s:v>4333.14</s:v>
+      </s:c>
       <s:c r="F60" s="14" t="n">
         <s:v>10698.8</s:v>
       </s:c>
@@ -2937,7 +3055,9 @@
       <s:c r="D61" s="12" t="n">
         <s:v>28131.9</s:v>
       </s:c>
-      <s:c r="E61" s="13"/>
+      <s:c r="E61" s="13" t="n">
+        <s:v>4310.95</s:v>
+      </s:c>
       <s:c r="F61" s="14" t="n">
         <s:v>10136.5</s:v>
       </s:c>
@@ -2963,7 +3083,9 @@
       <s:c r="D62" s="12" t="n">
         <s:v>28341.8</s:v>
       </s:c>
-      <s:c r="E62" s="13"/>
+      <s:c r="E62" s="13" t="n">
+        <s:v>4420</s:v>
+      </s:c>
       <s:c r="F62" s="14" t="n">
         <s:v>9633.7</s:v>
       </s:c>
@@ -2989,7 +3111,9 @@
       <s:c r="D63" s="12" t="n">
         <s:v>29270.6</s:v>
       </s:c>
-      <s:c r="E63" s="13"/>
+      <s:c r="E63" s="13" t="n">
+        <s:v>4837.65</s:v>
+      </s:c>
       <s:c r="F63" s="14" t="n">
         <s:v>8593.7</s:v>
       </s:c>
@@ -3015,7 +3139,9 @@
       <s:c r="D64" s="12" t="n">
         <s:v>30055.3</s:v>
       </s:c>
-      <s:c r="E64" s="13"/>
+      <s:c r="E64" s="13" t="n">
+        <s:v>5295.01</s:v>
+      </s:c>
       <s:c r="F64" s="14" t="n">
         <s:v>7979.3</s:v>
       </s:c>
@@ -3041,7 +3167,9 @@
       <s:c r="D65" s="12" t="n">
         <s:v>30583.7</s:v>
       </s:c>
-      <s:c r="E65" s="13"/>
+      <s:c r="E65" s="13" t="n">
+        <s:v>6000.27</s:v>
+      </s:c>
       <s:c r="F65" s="14" t="n">
         <s:v>7344</s:v>
       </s:c>
@@ -3067,7 +3195,9 @@
       <s:c r="D66" s="12" t="n">
         <s:v>31672.1</s:v>
       </s:c>
-      <s:c r="E66" s="13"/>
+      <s:c r="E66" s="13" t="n">
+        <s:v>6700.94</s:v>
+      </s:c>
       <s:c r="F66" s="14" t="n">
         <s:v>6221.2</s:v>
       </s:c>
@@ -3093,7 +3223,9 @@
       <s:c r="D67" s="12" t="n">
         <s:v>32459.7</s:v>
       </s:c>
-      <s:c r="E67" s="13"/>
+      <s:c r="E67" s="13" t="n">
+        <s:v>7202.32</s:v>
+      </s:c>
       <s:c r="F67" s="14" t="n">
         <s:v>5587.1</s:v>
       </s:c>
@@ -3119,7 +3251,9 @@
       <s:c r="D68" s="12" t="n">
         <s:v>33425.8</s:v>
       </s:c>
-      <s:c r="E68" s="13"/>
+      <s:c r="E68" s="13" t="n">
+        <s:v>7681.91</s:v>
+      </s:c>
       <s:c r="F68" s="14" t="n">
         <s:v>4872.9</s:v>
       </s:c>
@@ -3145,7 +3279,9 @@
       <s:c r="D69" s="12" t="n">
         <s:v>34781.3</s:v>
       </s:c>
-      <s:c r="E69" s="13"/>
+      <s:c r="E69" s="13" t="n">
+        <s:v>8198.39</s:v>
+      </s:c>
       <s:c r="F69" s="14" t="n">
         <s:v>3958.2</s:v>
       </s:c>
@@ -3171,7 +3307,9 @@
       <s:c r="D70" s="12" t="n">
         <s:v>35930.5</s:v>
       </s:c>
-      <s:c r="E70" s="13"/>
+      <s:c r="E70" s="13" t="n">
+        <s:v>8662.6</s:v>
+      </s:c>
       <s:c r="F70" s="14" t="n">
         <s:v>3213.6</s:v>
       </s:c>
@@ -3197,7 +3335,9 @@
       <s:c r="D71" s="12" t="n">
         <s:v>36662.2</s:v>
       </s:c>
-      <s:c r="E71" s="13"/>
+      <s:c r="E71" s="13" t="n">
+        <s:v>8797.23</s:v>
+      </s:c>
       <s:c r="F71" s="14" t="n">
         <s:v>2495.8</s:v>
       </s:c>
@@ -3223,7 +3363,9 @@
       <s:c r="D72" s="12" t="n">
         <s:v>37310.9</s:v>
       </s:c>
-      <s:c r="E72" s="13"/>
+      <s:c r="E72" s="13" t="n">
+        <s:v>8812.05</s:v>
+      </s:c>
       <s:c r="F72" s="14" t="n">
         <s:v>1830.8</s:v>
       </s:c>
@@ -3249,7 +3391,9 @@
       <s:c r="D73" s="12" t="n">
         <s:v>37248</s:v>
       </s:c>
-      <s:c r="E73" s="13"/>
+      <s:c r="E73" s="13" t="n">
+        <s:v>8828.74</s:v>
+      </s:c>
       <s:c r="F73" s="14" t="n">
         <s:v>1296</s:v>
       </s:c>
@@ -3275,7 +3419,9 @@
       <s:c r="D74" s="12" t="n">
         <s:v>37578.5</s:v>
       </s:c>
-      <s:c r="E74" s="13"/>
+      <s:c r="E74" s="13" t="n">
+        <s:v>8857.03</s:v>
+      </s:c>
       <s:c r="F74" s="14" t="n">
         <s:v>964.3</s:v>
       </s:c>
@@ -3301,7 +3447,9 @@
       <s:c r="D75" s="12" t="n">
         <s:v>37357</s:v>
       </s:c>
-      <s:c r="E75" s="13"/>
+      <s:c r="E75" s="13" t="n">
+        <s:v>8888.76</s:v>
+      </s:c>
       <s:c r="F75" s="14" t="n">
         <s:v>766.7</s:v>
       </s:c>
@@ -3327,7 +3475,9 @@
       <s:c r="D76" s="12" t="n">
         <s:v>36822.9</s:v>
       </s:c>
-      <s:c r="E76" s="13"/>
+      <s:c r="E76" s="13" t="n">
+        <s:v>8877.33</s:v>
+      </s:c>
       <s:c r="F76" s="14" t="n">
         <s:v>615.6</s:v>
       </s:c>
@@ -3353,7 +3503,9 @@
       <s:c r="D77" s="12" t="n">
         <s:v>37335.2</s:v>
       </s:c>
-      <s:c r="E77" s="13"/>
+      <s:c r="E77" s="13" t="n">
+        <s:v>8870.4</s:v>
+      </s:c>
       <s:c r="F77" s="14" t="n">
         <s:v>646.1</s:v>
       </s:c>
@@ -3379,7 +3531,9 @@
       <s:c r="D78" s="12" t="n">
         <s:v>36841.6</s:v>
       </s:c>
-      <s:c r="E78" s="13"/>
+      <s:c r="E78" s="13" t="n">
+        <s:v>8866.05</s:v>
+      </s:c>
       <s:c r="F78" s="14" t="n">
         <s:v>688.4</s:v>
       </s:c>
@@ -3405,7 +3559,9 @@
       <s:c r="D79" s="12" t="n">
         <s:v>36272.1</s:v>
       </s:c>
-      <s:c r="E79" s="13"/>
+      <s:c r="E79" s="13" t="n">
+        <s:v>8867.44</s:v>
+      </s:c>
       <s:c r="F79" s="14" t="n">
         <s:v>727.7</s:v>
       </s:c>
@@ -3431,7 +3587,9 @@
       <s:c r="D80" s="12" t="n">
         <s:v>36075.1</s:v>
       </s:c>
-      <s:c r="E80" s="13"/>
+      <s:c r="E80" s="13" t="n">
+        <s:v>8872.02</s:v>
+      </s:c>
       <s:c r="F80" s="14" t="n">
         <s:v>781.1</s:v>
       </s:c>
@@ -3457,7 +3615,9 @@
       <s:c r="D81" s="12" t="n">
         <s:v>35606.8</s:v>
       </s:c>
-      <s:c r="E81" s="13"/>
+      <s:c r="E81" s="13" t="n">
+        <s:v>8878.81</s:v>
+      </s:c>
       <s:c r="F81" s="14" t="n">
         <s:v>813.1</s:v>
       </s:c>
@@ -3483,7 +3643,9 @@
       <s:c r="D82" s="12" t="n">
         <s:v>35014.9</s:v>
       </s:c>
-      <s:c r="E82" s="13"/>
+      <s:c r="E82" s="13" t="n">
+        <s:v>8875.88</s:v>
+      </s:c>
       <s:c r="F82" s="14" t="n">
         <s:v>890.1</s:v>
       </s:c>
@@ -3509,7 +3671,9 @@
       <s:c r="D83" s="12" t="n">
         <s:v>34671.3</s:v>
       </s:c>
-      <s:c r="E83" s="13"/>
+      <s:c r="E83" s="13" t="n">
+        <s:v>8874.76</s:v>
+      </s:c>
       <s:c r="F83" s="14" t="n">
         <s:v>905.7</s:v>
       </s:c>
@@ -3535,7 +3699,9 @@
       <s:c r="D84" s="12" t="n">
         <s:v>34660.2</s:v>
       </s:c>
-      <s:c r="E84" s="13"/>
+      <s:c r="E84" s="13" t="n">
+        <s:v>8876.79</s:v>
+      </s:c>
       <s:c r="F84" s="14" t="n">
         <s:v>957.6</s:v>
       </s:c>
@@ -3561,7 +3727,9 @@
       <s:c r="D85" s="12" t="n">
         <s:v>34285.2</s:v>
       </s:c>
-      <s:c r="E85" s="13"/>
+      <s:c r="E85" s="13" t="n">
+        <s:v>8875.77</s:v>
+      </s:c>
       <s:c r="F85" s="14" t="n">
         <s:v>988.3</s:v>
       </s:c>
@@ -3587,7 +3755,9 @@
       <s:c r="D86" s="12" t="n">
         <s:v>33958.5</s:v>
       </s:c>
-      <s:c r="E86" s="13"/>
+      <s:c r="E86" s="13" t="n">
+        <s:v>8859.9</s:v>
+      </s:c>
       <s:c r="F86" s="14" t="n">
         <s:v>1043.1</s:v>
       </s:c>
@@ -3613,7 +3783,9 @@
       <s:c r="D87" s="12" t="n">
         <s:v>33657</s:v>
       </s:c>
-      <s:c r="E87" s="13"/>
+      <s:c r="E87" s="13" t="n">
+        <s:v>8859.27</s:v>
+      </s:c>
       <s:c r="F87" s="14" t="n">
         <s:v>1066.9</s:v>
       </s:c>
@@ -3639,7 +3811,9 @@
       <s:c r="D88" s="12" t="n">
         <s:v>33385.9</s:v>
       </s:c>
-      <s:c r="E88" s="13"/>
+      <s:c r="E88" s="13" t="n">
+        <s:v>8856.46</s:v>
+      </s:c>
       <s:c r="F88" s="14" t="n">
         <s:v>1044.6</s:v>
       </s:c>
@@ -3665,7 +3839,9 @@
       <s:c r="D89" s="12" t="n">
         <s:v>33043.4</s:v>
       </s:c>
-      <s:c r="E89" s="13"/>
+      <s:c r="E89" s="13" t="n">
+        <s:v>8854.96</s:v>
+      </s:c>
       <s:c r="F89" s="14" t="n">
         <s:v>984.4</s:v>
       </s:c>
@@ -3691,7 +3867,9 @@
       <s:c r="D90" s="12" t="n">
         <s:v>32765.2</s:v>
       </s:c>
-      <s:c r="E90" s="13"/>
+      <s:c r="E90" s="13" t="n">
+        <s:v>8803.33</s:v>
+      </s:c>
       <s:c r="F90" s="14" t="n">
         <s:v>938.2</s:v>
       </s:c>
@@ -3717,7 +3895,9 @@
       <s:c r="D91" s="12" t="n">
         <s:v>32586.9</s:v>
       </s:c>
-      <s:c r="E91" s="13"/>
+      <s:c r="E91" s="13" t="n">
+        <s:v>8803.3</s:v>
+      </s:c>
       <s:c r="F91" s="14" t="n">
         <s:v>897.7</s:v>
       </s:c>
@@ -3743,7 +3923,9 @@
       <s:c r="D92" s="12" t="n">
         <s:v>31863.7</s:v>
       </s:c>
-      <s:c r="E92" s="13"/>
+      <s:c r="E92" s="13" t="n">
+        <s:v>8799.05</s:v>
+      </s:c>
       <s:c r="F92" s="14" t="n">
         <s:v>863</s:v>
       </s:c>
@@ -3769,7 +3951,9 @@
       <s:c r="D93" s="12" t="n">
         <s:v>31330.7</s:v>
       </s:c>
-      <s:c r="E93" s="13"/>
+      <s:c r="E93" s="13" t="n">
+        <s:v>8796.74</s:v>
+      </s:c>
       <s:c r="F93" s="14" t="n">
         <s:v>829.6</s:v>
       </s:c>
@@ -3795,7 +3979,9 @@
       <s:c r="D94" s="12" t="n">
         <s:v>30595.8</s:v>
       </s:c>
-      <s:c r="E94" s="13"/>
+      <s:c r="E94" s="13" t="n">
+        <s:v>8797.29</s:v>
+      </s:c>
       <s:c r="F94" s="14" t="n">
         <s:v>828.4</s:v>
       </s:c>
@@ -3821,7 +4007,9 @@
       <s:c r="D95" s="12" t="n">
         <s:v>30061.5</s:v>
       </s:c>
-      <s:c r="E95" s="13"/>
+      <s:c r="E95" s="13" t="n">
+        <s:v>8795.57</s:v>
+      </s:c>
       <s:c r="F95" s="14" t="n">
         <s:v>831</s:v>
       </s:c>
@@ -3847,7 +4035,9 @@
       <s:c r="D96" s="12" t="n">
         <s:v>29568.1</s:v>
       </s:c>
-      <s:c r="E96" s="13"/>
+      <s:c r="E96" s="13" t="n">
+        <s:v>8791.44</s:v>
+      </s:c>
       <s:c r="F96" s="14" t="n">
         <s:v>845.9</s:v>
       </s:c>
@@ -3875,7 +4065,9 @@
       <s:c r="D97" s="12" t="n">
         <s:v>29535.8</s:v>
       </s:c>
-      <s:c r="E97" s="13"/>
+      <s:c r="E97" s="13" t="n">
+        <s:v>8791.87</s:v>
+      </s:c>
       <s:c r="F97" s="14" t="n">
         <s:v>857.2</s:v>
       </s:c>
